--- a/InputData/web-app/BpTPEU/BTU per Total Primary Energy Unit.xlsx
+++ b/InputData/web-app/BpTPEU/BTU per Total Primary Energy Unit.xlsx
@@ -1,27 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24827"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CodeRepositories\eps-us\InputData\web-app\BpTPEU\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-southkorea\InputData\web-app\BpTPEU\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8958BCBB-A63B-44A2-ABD6-4D5A8FCCE5F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="720" yWindow="390" windowWidth="27555" windowHeight="14100"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="BpTPEU-large" sheetId="2" r:id="rId2"/>
     <sheet name="BpTPEU-small" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029" iterate="1" iterateDelta="1.0000000000000001E-5"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="19">
   <si>
     <t>Source:</t>
   </si>
@@ -38,12 +50,6 @@
     <t>For the U.S.:</t>
   </si>
   <si>
-    <t>large primary energy output unit</t>
-  </si>
-  <si>
-    <t>small primary energy output unit</t>
-  </si>
-  <si>
     <t>The large primary energy output unit (used in totals graphs) is: quadrillion BTU</t>
   </si>
   <si>
@@ -55,12 +61,47 @@
   <si>
     <t>BpTPEU BTU per Small Primary Energy Unit</t>
   </si>
+  <si>
+    <t>btu to MJ</t>
+  </si>
+  <si>
+    <t>million TOE</t>
+  </si>
+  <si>
+    <t>For South Korea:</t>
+  </si>
+  <si>
+    <t>The large primary energy output unit (used in totals graphs) is: million TOE</t>
+  </si>
+  <si>
+    <t>The small primary energy output unit (used in energy intensity per unit GDP graphs) is: MJ</t>
+  </si>
+  <si>
+    <t>btu to million TOE</t>
+  </si>
+  <si>
+    <t>BTU per MJ</t>
+  </si>
+  <si>
+    <t>BTU per TOE</t>
+  </si>
+  <si>
+    <t>https://en.wikipedia.org/wiki/Tonne_of_oil_equivalent#:~:text=1%20toe%20%3D%2039%2C683%2C207.2%20British%20thermal%20units%20(BTU)</t>
+  </si>
+  <si>
+    <t>https://www.unitconverters.net/energy/megajoule-to-btu-it.htm</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="3">
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0.0000000000_);_(* \(#,##0.0000000000\);_(* &quot;-&quot;??_);_(@_)"/>
+  </numFmts>
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -70,6 +111,21 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -94,10 +150,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -105,8 +162,13 @@
     </xf>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -198,6 +260,23 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -233,6 +312,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -408,18 +504,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B12"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.28515625" customWidth="1"/>
+    <col min="2" max="2" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.7109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -445,12 +546,66 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>8</v>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B18" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="3">
+        <v>39683207.200000003</v>
+      </c>
+      <c r="D20" s="8"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>10</v>
+      </c>
+      <c r="B21" s="6">
+        <f>10^6</f>
+        <v>1000000</v>
+      </c>
+      <c r="C21" s="7"/>
+      <c r="D21" s="8"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23">
+        <v>947.81712000000005</v>
+      </c>
+      <c r="D23" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -460,7 +615,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
@@ -472,7 +627,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B1" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -480,8 +635,8 @@
         <v>2</v>
       </c>
       <c r="B2" s="3">
-        <f>10^15</f>
-        <v>1000000000000000</v>
+        <f>About!B20*About!B21</f>
+        <v>39683207200000</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -496,7 +651,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
@@ -508,7 +663,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B1" s="2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -516,8 +671,8 @@
         <v>2</v>
       </c>
       <c r="B2" s="4">
-        <f>10^3</f>
-        <v>1000</v>
+        <f>About!$B$23</f>
+        <v>947.81712000000005</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -529,4 +684,175 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E59C87379D9A4242BB3A95F198D6F941" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="07a235b40ffe2d9a960bde50f6511605">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="40f4d404-d193-41dc-bb72-733c1e774208" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="485fc8e6f691b86ce0aee9b7e82feca0" ns2:_="">
+    <xsd:import namespace="40f4d404-d193-41dc-bb72-733c1e774208"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="40f4d404-d193-41dc-bb72-733c1e774208" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8131C158-94C5-4DAF-987C-F59BBF5BDA7D}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A4AF44AE-CBB0-47EE-8E2A-87439A6465AC}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA3F16E4-7D00-4CEE-9C2C-32F1C8CCCCCE}"/>
 </file>